--- a/artfynd/A 56916-2025 artfynd.xlsx
+++ b/artfynd/A 56916-2025 artfynd.xlsx
@@ -1326,7 +1326,7 @@
         <v>123601979</v>
       </c>
       <c r="B8" t="n">
-        <v>57966</v>
+        <v>58021</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 56916-2025 artfynd.xlsx
+++ b/artfynd/A 56916-2025 artfynd.xlsx
@@ -1326,7 +1326,7 @@
         <v>123601979</v>
       </c>
       <c r="B8" t="n">
-        <v>58021</v>
+        <v>58034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 56916-2025 artfynd.xlsx
+++ b/artfynd/A 56916-2025 artfynd.xlsx
@@ -1326,7 +1326,7 @@
         <v>123601979</v>
       </c>
       <c r="B8" t="n">
-        <v>58034</v>
+        <v>58036</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 56916-2025 artfynd.xlsx
+++ b/artfynd/A 56916-2025 artfynd.xlsx
@@ -1358,11 +1358,7 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>

--- a/artfynd/A 56916-2025 artfynd.xlsx
+++ b/artfynd/A 56916-2025 artfynd.xlsx
@@ -1326,7 +1326,7 @@
         <v>123601979</v>
       </c>
       <c r="B8" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 56916-2025 artfynd.xlsx
+++ b/artfynd/A 56916-2025 artfynd.xlsx
@@ -1326,7 +1326,7 @@
         <v>123601979</v>
       </c>
       <c r="B8" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 56916-2025 artfynd.xlsx
+++ b/artfynd/A 56916-2025 artfynd.xlsx
@@ -1326,7 +1326,7 @@
         <v>123601979</v>
       </c>
       <c r="B8" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 56916-2025 artfynd.xlsx
+++ b/artfynd/A 56916-2025 artfynd.xlsx
@@ -1326,7 +1326,7 @@
         <v>123601979</v>
       </c>
       <c r="B8" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
